--- a/data/office/q1-sales-pipeline.xlsx
+++ b/data/office/q1-sales-pipeline.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Open Opportunities" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Closed Won Q1 2026" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Q2 Forecast by Month" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open Opportunities" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Closed Won Q1 2026" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q2 Forecast by Month" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,8 +19,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="$#,##0"/>
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -60,14 +60,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -437,15 +434,15 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="7" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="19" customWidth="1" min="7" max="7"/>
-    <col width="17" customWidth="1" min="8" max="8"/>
-    <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
     <col width="19" customWidth="1" min="12" max="12"/>
   </cols>
@@ -478,27 +475,27 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>Unit Price (USD)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>Amount (USD)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Stage</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Win Probability</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Forecast Category</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Created Date</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -515,48 +512,48 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>OPP-1041</t>
+          <t>OPP-1201</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Hendricks Chemical</t>
+          <t>Quennick</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>XT-9 site rollout, 60 units with installation and commissioning</t>
+          <t>GX-7 expansion order, second site</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>XT-9</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="F2" s="4" t="n">
-        <v>226000</v>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
+          <t>GX-7</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>192.6</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>57780</v>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>Negotiation</t>
         </is>
       </c>
-      <c r="H2" s="5" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="I2" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>Commit</t>
         </is>
       </c>
-      <c r="J2" s="6" t="n">
-        <v>45936</v>
-      </c>
-      <c r="K2" s="6" t="n">
-        <v>46136</v>
+      <c r="K2" s="3" t="n">
+        <v>46171</v>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
@@ -567,48 +564,48 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>OPP-1042</t>
+          <t>OPP-1202</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Tallis Water Authority</t>
+          <t>Quennick</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Reservoir level monitoring phase 2</t>
+          <t>MX-3 spares pool</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>XT-9</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>160</v>
-      </c>
-      <c r="F3" s="4" t="n">
-        <v>232000</v>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
+          <t>MX-3</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>238.5</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>9540</v>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Proposal</t>
         </is>
       </c>
-      <c r="H3" s="5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" s="2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>Best Case</t>
         </is>
       </c>
-      <c r="J3" s="6" t="n">
-        <v>45999</v>
-      </c>
-      <c r="K3" s="6" t="n">
-        <v>46171</v>
+      <c r="K3" s="3" t="n">
+        <v>46192</v>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
@@ -619,256 +616,256 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>OPP-1043</t>
+          <t>OPP-1203</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Thornbury Power</t>
+          <t>Hessanby Dynamics</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Cooling tower vibration and level monitoring</t>
+          <t>GX-7 follow-on order</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>FieldSense 200</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>130</v>
-      </c>
-      <c r="F4" s="4" t="n">
-        <v>104000</v>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+          <t>GX-7</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>198</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>23760</v>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Proposal</t>
         </is>
       </c>
-      <c r="H4" s="5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>Best Case</t>
         </is>
       </c>
-      <c r="J4" s="6" t="n">
-        <v>46027</v>
-      </c>
-      <c r="K4" s="6" t="n">
-        <v>46192</v>
+      <c r="K4" s="3" t="n">
+        <v>46185</v>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>Elena</t>
+          <t>Jamal</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>OPP-1044</t>
+          <t>OPP-1204</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Grayson Textiles</t>
+          <t>Ivelmoor Group</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Conveyor presence detection</t>
+          <t>GX-7 plant two rollout</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>ProximaSense X4</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>80</v>
-      </c>
-      <c r="F5" s="4" t="n">
-        <v>4640</v>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Qualification</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+          <t>GX-7</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>220</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>192.6</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>42372</v>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Evaluation</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>Pipeline</t>
         </is>
       </c>
-      <c r="J5" s="6" t="n">
-        <v>46029</v>
-      </c>
-      <c r="K5" s="6" t="n">
-        <v>46162</v>
+      <c r="K5" s="3" t="n">
+        <v>46199</v>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>Jamal</t>
+          <t>Elena</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>OPP-1045</t>
+          <t>OPP-1205</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Estavan Chemicals</t>
+          <t>Ivelmoor Group</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Rotating equipment monitoring</t>
+          <t>RV-2 pilot</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>FieldSense 200</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="F6" s="4" t="n">
-        <v>12600</v>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+          <t>RV-2</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>189</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>5670</v>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Qualification</t>
         </is>
       </c>
-      <c r="H6" s="5" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>Pipeline</t>
         </is>
       </c>
-      <c r="J6" s="6" t="n">
-        <v>46032</v>
-      </c>
-      <c r="K6" s="6" t="n">
-        <v>46178</v>
+      <c r="K6" s="3" t="n">
+        <v>46220</v>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>Elena</t>
+          <t>Jamal</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>OPP-1046</t>
+          <t>OPP-1206</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Meridian Industrial</t>
+          <t>Trellisar</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>XT-9 reorder with commissioning, three plants</t>
+          <t>GX-7 line expansion</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>XT-9</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>120</v>
-      </c>
-      <c r="F7" s="4" t="n">
-        <v>186000</v>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+          <t>GX-7</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>150</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>192.6</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>28890</v>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Negotiation</t>
         </is>
       </c>
-      <c r="H7" s="5" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>Commit</t>
         </is>
       </c>
-      <c r="J7" s="6" t="n">
-        <v>46035</v>
-      </c>
-      <c r="K7" s="6" t="n">
-        <v>46157</v>
+      <c r="K7" s="3" t="n">
+        <v>46136</v>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>Elena</t>
+          <t>Jamal</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>OPP-1047</t>
+          <t>OPP-1207</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Pellham Steel</t>
+          <t>Trellisar</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>XT-9 ladle and tundish level monitoring with commissioning</t>
+          <t>RV-2 early adopter order</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>XT-9</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="n">
-        <v>160</v>
-      </c>
-      <c r="F8" s="4" t="n">
-        <v>254000</v>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>Demo / evaluation</t>
-        </is>
-      </c>
-      <c r="H8" s="5" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+          <t>RV-2</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>189</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>11340</v>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Proposal</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>Best Case</t>
         </is>
       </c>
-      <c r="J8" s="6" t="n">
-        <v>46041</v>
-      </c>
-      <c r="K8" s="6" t="n">
-        <v>46178</v>
+      <c r="K8" s="3" t="n">
+        <v>46185</v>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
@@ -879,100 +876,100 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>OPP-1048</t>
+          <t>OPP-1208</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Sable Creek Gas</t>
+          <t>Oskerry Systems</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>XT-9 wellhead expansion, east field</t>
+          <t>RV-2 first production order</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>XT-9</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="n">
+          <t>RV-2</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
         <v>120</v>
       </c>
-      <c r="F9" s="4" t="n">
-        <v>174000</v>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>Discovery</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>Best Case</t>
-        </is>
-      </c>
-      <c r="J9" s="6" t="n">
-        <v>46042</v>
-      </c>
-      <c r="K9" s="6" t="n">
-        <v>46192</v>
+      <c r="F9" s="2" t="n">
+        <v>189</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>22680</v>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Negotiation</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="n">
+        <v>46178</v>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>Elena</t>
+          <t>Jamal</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>OPP-1049</t>
+          <t>OPP-1209</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Holloway Fertilizer</t>
+          <t>Oskerry Systems</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>FieldSense 200 pilot</t>
+          <t>RV-2 second site</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>FieldSense 200</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="F10" s="4" t="n">
-        <v>24000</v>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>Qualification</t>
-        </is>
-      </c>
-      <c r="H10" s="5" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
+          <t>RV-2</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>189</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>15120</v>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Evaluation</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>Pipeline</t>
         </is>
       </c>
-      <c r="J10" s="6" t="n">
-        <v>46043</v>
-      </c>
-      <c r="K10" s="6" t="n">
-        <v>46198</v>
+      <c r="K10" s="3" t="n">
+        <v>46227</v>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
@@ -983,152 +980,152 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>OPP-1050</t>
+          <t>OPP-1210</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Barrow Tide Ports</t>
+          <t>Fenstad Systems</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Packaging line retrofit</t>
+          <t>GX-7 EU deployment</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>ProximaSense X4</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="F11" s="4" t="n">
-        <v>5200</v>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+          <t>GX-7</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>260</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>215.1</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>55926</v>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>Qualification</t>
         </is>
       </c>
-      <c r="H11" s="5" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>Pipeline</t>
         </is>
       </c>
-      <c r="J11" s="6" t="n">
-        <v>46044</v>
-      </c>
-      <c r="K11" s="6" t="n">
-        <v>46161</v>
+      <c r="K11" s="3" t="n">
+        <v>46325</v>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>Jamal</t>
+          <t>Elena</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>OPP-1051</t>
+          <t>OPP-1211</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Wexford Sugar</t>
+          <t>Pellowdine Industrial</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Plant-wide sensor refresh</t>
+          <t>GX-7 multi-site standardization</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>XT-9</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="F12" s="4" t="n">
-        <v>21750</v>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>Qualification</t>
-        </is>
-      </c>
-      <c r="H12" s="5" t="n">
+          <t>GX-7</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>215.1</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>86040</v>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Discovery</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="n">
         <v>0.1</v>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>Pipeline</t>
         </is>
       </c>
-      <c r="J12" s="6" t="n">
-        <v>46045</v>
-      </c>
-      <c r="K12" s="6" t="n">
-        <v>46162</v>
+      <c r="K12" s="3" t="n">
+        <v>46472</v>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>Jamal</t>
+          <t>Elena</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>OPP-1052</t>
+          <t>OPP-1212</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Yardley Grain</t>
+          <t>Drossick</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Rotating equipment monitoring</t>
+          <t>GX-7 replacement of legacy units</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>FieldSense 200</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="F13" s="4" t="n">
-        <v>20000</v>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>Qualification</t>
-        </is>
-      </c>
-      <c r="H13" s="5" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>Pipeline</t>
-        </is>
-      </c>
-      <c r="J13" s="6" t="n">
-        <v>46046</v>
-      </c>
-      <c r="K13" s="6" t="n">
-        <v>46176</v>
+          <t>GX-7</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>175.48</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>15793.2</v>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Proposal</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="n">
+        <v>46157</v>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
@@ -1139,48 +1136,48 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>OPP-1053</t>
+          <t>OPP-1213</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Ironbridge Foundry</t>
+          <t>Tessivex</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Process line upgrade</t>
+          <t>GX-7 retrofit, phase 1</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>FieldSense 200</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="F14" s="4" t="n">
-        <v>32000</v>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>Qualification</t>
-        </is>
-      </c>
-      <c r="H14" s="5" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+          <t>GX-7</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>181.9</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>13642.5</v>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Evaluation</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>Pipeline</t>
         </is>
       </c>
-      <c r="J14" s="6" t="n">
-        <v>46047</v>
-      </c>
-      <c r="K14" s="6" t="n">
-        <v>46188</v>
+      <c r="K14" s="3" t="n">
+        <v>46164</v>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
@@ -1191,48 +1188,48 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>OPP-1054</t>
+          <t>OPP-1214</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Quenby Plastics</t>
+          <t>Tessivex</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Rotating equipment monitoring</t>
+          <t>GX-7 retrofit, phase 2</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>FieldSense 200</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="F15" s="4" t="n">
-        <v>8400</v>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>Qualification</t>
-        </is>
-      </c>
-      <c r="H15" s="5" t="n">
+          <t>GX-7</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>110</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>215.1</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>23661</v>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>Discovery</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="n">
         <v>0.1</v>
       </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="J15" s="2" t="inlineStr">
         <is>
           <t>Pipeline</t>
         </is>
       </c>
-      <c r="J15" s="6" t="n">
-        <v>46049</v>
-      </c>
-      <c r="K15" s="6" t="n">
-        <v>46202</v>
+      <c r="K15" s="3" t="n">
+        <v>46290</v>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
@@ -1243,100 +1240,100 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>OPP-1055</t>
+          <t>OPP-1215</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Gilmour Distilling</t>
+          <t>Kilnwarden Utilities</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Plant-wide sensor refresh</t>
+          <t>MX-3 substation refresh</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>XT-9</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="F16" s="4" t="n">
-        <v>6080</v>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>Qualification</t>
-        </is>
-      </c>
-      <c r="H16" s="5" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>Pipeline</t>
-        </is>
-      </c>
-      <c r="J16" s="6" t="n">
-        <v>46050</v>
-      </c>
-      <c r="K16" s="6" t="n">
-        <v>46154</v>
+          <t>MX-3</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>180</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>238.5</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>42930</v>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>Proposal</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="n">
+        <v>46150</v>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>Jamal</t>
+          <t>Elena</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>OPP-1056</t>
+          <t>OPP-1216</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Kinsale Biofuels</t>
+          <t>Kilnwarden Utilities</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Level sensing retrofit</t>
+          <t>GX-7 pump station pilot</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>XT-9</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="F17" s="4" t="n">
-        <v>9120</v>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+          <t>GX-7</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>239</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>5736</v>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>Qualification</t>
         </is>
       </c>
-      <c r="H17" s="5" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
         <is>
           <t>Pipeline</t>
         </is>
       </c>
-      <c r="J17" s="6" t="n">
-        <v>46050</v>
-      </c>
-      <c r="K17" s="6" t="n">
-        <v>46195</v>
+      <c r="K17" s="3" t="n">
+        <v>46203</v>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
@@ -1347,48 +1344,48 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>OPP-1057</t>
+          <t>OPP-1217</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Orland Pulp</t>
+          <t>Sorrelby Water</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Packaging line retrofit</t>
+          <t>GX-7 treatment works, phase 2</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>ProximaSense X4</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="F18" s="4" t="n">
-        <v>2320</v>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>Qualification</t>
-        </is>
-      </c>
-      <c r="H18" s="5" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>Pipeline</t>
-        </is>
-      </c>
-      <c r="J18" s="6" t="n">
-        <v>46050</v>
-      </c>
-      <c r="K18" s="6" t="n">
-        <v>46195</v>
+          <t>GX-7</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>140</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>192.6</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>26964</v>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>Negotiation</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="n">
+        <v>46129</v>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
@@ -1399,100 +1396,100 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>OPP-1058</t>
+          <t>OPP-1218</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Kessler Paper Mill</t>
+          <t>Sorrelby Water</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>FieldSense 200 pilot</t>
+          <t>RV-2 evaluation units</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>FieldSense 200</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="F19" s="4" t="n">
-        <v>24000</v>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>Qualification</t>
-        </is>
-      </c>
-      <c r="H19" s="5" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
+          <t>RV-2</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>209</v>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>2508</v>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>Evaluation</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>Pipeline</t>
         </is>
       </c>
-      <c r="J19" s="6" t="n">
-        <v>46052</v>
-      </c>
-      <c r="K19" s="6" t="n">
-        <v>46198</v>
+      <c r="K19" s="3" t="n">
+        <v>46213</v>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>Elena</t>
+          <t>Jamal</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>OPP-1059</t>
+          <t>OPP-1219</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Larkspur Semiconductors</t>
+          <t>Pemberlith Foods</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>FieldSense 200 pilot</t>
+          <t>MX-3 packing line controls</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>FieldSense 200</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="F20" s="4" t="n">
-        <v>8400</v>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>Qualification</t>
-        </is>
-      </c>
-      <c r="H20" s="5" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
+          <t>MX-3</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>238.5</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>22657.5</v>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>Evaluation</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
         <is>
           <t>Pipeline</t>
         </is>
       </c>
-      <c r="J20" s="6" t="n">
-        <v>46052</v>
-      </c>
-      <c r="K20" s="6" t="n">
-        <v>46164</v>
+      <c r="K20" s="3" t="n">
+        <v>46171</v>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
@@ -1503,48 +1500,48 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>OPP-1060</t>
+          <t>OPP-1220</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Harrowgate Cement</t>
+          <t>Pemberlith Foods</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Kiln feed silo instrumentation</t>
+          <t>GX-7 cold store rollout</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>XT-9</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="n">
-        <v>80</v>
-      </c>
-      <c r="F21" s="4" t="n">
-        <v>116000</v>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
+          <t>GX-7</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>215.1</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>12906</v>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>Discovery</t>
         </is>
       </c>
-      <c r="H21" s="5" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>Best Case</t>
-        </is>
-      </c>
-      <c r="J21" s="6" t="n">
-        <v>46057</v>
-      </c>
-      <c r="K21" s="6" t="n">
-        <v>46199</v>
+      <c r="I21" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>Pipeline</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="n">
+        <v>46262</v>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
@@ -1555,48 +1552,48 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>OPP-1061</t>
+          <t>OPP-1221</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Vickery Ceramics</t>
+          <t>Callowmere Packaging</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Rotating equipment monitoring</t>
+          <t>MX-3 line two</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>FieldSense 200</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="F22" s="4" t="n">
-        <v>24000</v>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>Qualification</t>
-        </is>
-      </c>
-      <c r="H22" s="5" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>Pipeline</t>
-        </is>
-      </c>
-      <c r="J22" s="6" t="n">
-        <v>46058</v>
-      </c>
-      <c r="K22" s="6" t="n">
-        <v>46163</v>
+          <t>MX-3</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>238.5</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>16695</v>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>Proposal</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="n">
+        <v>46142</v>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
@@ -1607,48 +1604,48 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>OPP-1062</t>
+          <t>OPP-1222</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Marrowfield Foods</t>
+          <t>Callowmere Packaging</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>FieldSense 200 plant-wide rollout</t>
+          <t>RV-2 trial</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>FieldSense 200</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="n">
-        <v>250</v>
-      </c>
-      <c r="F23" s="4" t="n">
-        <v>200000</v>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>Discovery</t>
-        </is>
-      </c>
-      <c r="H23" s="5" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>Best Case</t>
-        </is>
-      </c>
-      <c r="J23" s="6" t="n">
-        <v>46062</v>
-      </c>
-      <c r="K23" s="6" t="n">
-        <v>46203</v>
+          <t>RV-2</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>189</v>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>3780</v>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>Qualification</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>Pipeline</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="n">
+        <v>46199</v>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
@@ -1659,48 +1656,48 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>OPP-1063</t>
+          <t>OPP-1223</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Pinecrest Utilities</t>
+          <t>Tharnwick Rail</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Process line upgrade</t>
+          <t>GX-7 depot equipment</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>FieldSense 200</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="F24" s="4" t="n">
-        <v>8400</v>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+          <t>GX-7</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>215.1</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>43020</v>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>Qualification</t>
         </is>
       </c>
-      <c r="H24" s="5" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
+      <c r="I24" s="2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
         <is>
           <t>Pipeline</t>
         </is>
       </c>
-      <c r="J24" s="6" t="n">
-        <v>46063</v>
-      </c>
-      <c r="K24" s="6" t="n">
-        <v>46161</v>
+      <c r="K24" s="3" t="n">
+        <v>46248</v>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
@@ -1711,100 +1708,100 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>OPP-1064</t>
+          <t>OPP-1224</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Upton Cold Storage</t>
+          <t>Tharnwick Rail</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Outdoor tank level monitoring</t>
+          <t>MX-3 cabinet refresh</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>XT-9</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="F25" s="4" t="n">
-        <v>6080</v>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>Qualification</t>
-        </is>
-      </c>
-      <c r="H25" s="5" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
+          <t>MX-3</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>130</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>238.5</v>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>31005</v>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>Evaluation</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
         <is>
           <t>Pipeline</t>
         </is>
       </c>
-      <c r="J25" s="6" t="n">
-        <v>46063</v>
-      </c>
-      <c r="K25" s="6" t="n">
-        <v>46156</v>
+      <c r="K25" s="3" t="n">
+        <v>46192</v>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>Jamal</t>
+          <t>Elena</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>OPP-1065</t>
+          <t>OPP-1225</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Mercer Glassworks</t>
+          <t>Quennick</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Rotating equipment monitoring</t>
+          <t>GX-7 site three</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>FieldSense 200</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="F26" s="4" t="n">
-        <v>24000</v>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>Qualification</t>
-        </is>
-      </c>
-      <c r="H26" s="5" t="n">
+          <t>GX-7</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>150</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>215.1</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>32265</v>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>Discovery</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="n">
         <v>0.1</v>
       </c>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="J26" s="2" t="inlineStr">
         <is>
           <t>Pipeline</t>
         </is>
       </c>
-      <c r="J26" s="6" t="n">
-        <v>46064</v>
-      </c>
-      <c r="K26" s="6" t="n">
-        <v>46176</v>
+      <c r="K26" s="3" t="n">
+        <v>46283</v>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
@@ -1815,48 +1812,48 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>OPP-1066</t>
+          <t>OPP-1226</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Zellweger Coatings</t>
+          <t>Hessanby Dynamics</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Robot cell proximity sensing</t>
+          <t>RV-2 evaluation</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>ProximaSense X4</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="F27" s="4" t="n">
-        <v>5200</v>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
+          <t>RV-2</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>209</v>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>3135</v>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>Qualification</t>
         </is>
       </c>
-      <c r="H27" s="5" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
+      <c r="I27" s="2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
         <is>
           <t>Pipeline</t>
         </is>
       </c>
-      <c r="J27" s="6" t="n">
-        <v>46066</v>
-      </c>
-      <c r="K27" s="6" t="n">
-        <v>46161</v>
+      <c r="K27" s="3" t="n">
+        <v>46234</v>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
@@ -1867,48 +1864,48 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>OPP-1067</t>
+          <t>OPP-1227</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Fenwick Aggregates</t>
+          <t>Ivelmoor Group</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Plant-wide sensor refresh</t>
+          <t>MX-3 legacy replacement</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>XT-9</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="F28" s="4" t="n">
-        <v>6080</v>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>Qualification</t>
-        </is>
-      </c>
-      <c r="H28" s="5" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>Pipeline</t>
-        </is>
-      </c>
-      <c r="J28" s="6" t="n">
-        <v>46069</v>
-      </c>
-      <c r="K28" s="6" t="n">
-        <v>46185</v>
+          <t>MX-3</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>238.5</v>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>10732.5</v>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>Proposal</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="n">
+        <v>46157</v>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
@@ -1919,48 +1916,48 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>OPP-1068</t>
+          <t>OPP-1228</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Riverton Brewing</t>
+          <t>Trellisar</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Rotating equipment monitoring</t>
+          <t>MX-3 add-on</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>FieldSense 200</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="F29" s="4" t="n">
-        <v>6720</v>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>Qualification</t>
-        </is>
-      </c>
-      <c r="H29" s="5" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
+          <t>MX-3</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>238.5</v>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>8347.5</v>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>Evaluation</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
         <is>
           <t>Pipeline</t>
         </is>
       </c>
-      <c r="J29" s="6" t="n">
-        <v>46071</v>
-      </c>
-      <c r="K29" s="6" t="n">
-        <v>46184</v>
+      <c r="K29" s="3" t="n">
+        <v>46171</v>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
@@ -1971,48 +1968,48 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>OPP-1069</t>
+          <t>OPP-1229</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Ostergaard Process Systems</t>
+          <t>Drossick</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>FieldSense 200 multi-site expansion</t>
+          <t>RV-2 evaluation</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>FieldSense 200</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="n">
-        <v>265</v>
-      </c>
-      <c r="F30" s="4" t="n">
-        <v>212000</v>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>Proposal</t>
-        </is>
-      </c>
-      <c r="H30" s="5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>Best Case</t>
-        </is>
-      </c>
-      <c r="J30" s="6" t="n">
-        <v>46076</v>
-      </c>
-      <c r="K30" s="6" t="n">
-        <v>46185</v>
+          <t>RV-2</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>209</v>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>2090</v>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>Discovery</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>Pipeline</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="n">
+        <v>46255</v>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
@@ -2023,100 +2020,100 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>OPP-1070</t>
+          <t>OPP-1230</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Ashcombe Mining</t>
+          <t>Kilnwarden Utilities</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Process line upgrade</t>
+          <t>RV-2 remote sites</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>FieldSense 200</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="F31" s="4" t="n">
-        <v>24000</v>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>Qualification</t>
-        </is>
-      </c>
-      <c r="H31" s="5" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
+          <t>RV-2</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="F31" s="2" t="n">
+        <v>189</v>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>17010</v>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>Evaluation</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
         <is>
           <t>Pipeline</t>
         </is>
       </c>
-      <c r="J31" s="6" t="n">
-        <v>46080</v>
-      </c>
-      <c r="K31" s="6" t="n">
-        <v>46192</v>
+      <c r="K31" s="3" t="n">
+        <v>46206</v>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>Jamal</t>
+          <t>Elena</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>OPP-1071</t>
+          <t>OPP-1231</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Morrow Rail</t>
+          <t>Sorrelby Water</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Outdoor tank level monitoring</t>
+          <t>MX-3 spares</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>XT-9</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="F32" s="4" t="n">
-        <v>12160</v>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>Qualification</t>
-        </is>
-      </c>
-      <c r="H32" s="5" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>Pipeline</t>
-        </is>
-      </c>
-      <c r="J32" s="6" t="n">
-        <v>46089</v>
-      </c>
-      <c r="K32" s="6" t="n">
-        <v>46177</v>
+          <t>MX-3</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>238.5</v>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>5962.5</v>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>Negotiation</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="n">
+        <v>46122</v>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
@@ -2127,48 +2124,48 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>OPP-1072</t>
+          <t>OPP-1232</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Ellisford Chemicals</t>
+          <t>Pemberlith Foods</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Boiler room instrumentation</t>
+          <t>RV-2 warehouse pilot</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>XT-9</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="F33" s="4" t="n">
-        <v>14500</v>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
+          <t>RV-2</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>189</v>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>4725</v>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>Qualification</t>
         </is>
       </c>
-      <c r="H33" s="5" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
+      <c r="I33" s="2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
         <is>
           <t>Pipeline</t>
         </is>
       </c>
-      <c r="J33" s="6" t="n">
-        <v>46090</v>
-      </c>
-      <c r="K33" s="6" t="n">
-        <v>46167</v>
+      <c r="K33" s="3" t="n">
+        <v>46203</v>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
@@ -2179,48 +2176,48 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>OPP-1073</t>
+          <t>OPP-1233</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Nettleton Water</t>
+          <t>Callowmere Packaging</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Rotating equipment monitoring</t>
+          <t>GX-7 plant upgrade</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>FieldSense 200</t>
-        </is>
-      </c>
-      <c r="E34" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="F34" s="4" t="n">
-        <v>10080</v>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>Qualification</t>
-        </is>
-      </c>
-      <c r="H34" s="5" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
+          <t>GX-7</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>215.1</v>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>18283.5</v>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>Evaluation</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
         <is>
           <t>Pipeline</t>
         </is>
       </c>
-      <c r="J34" s="6" t="n">
-        <v>46090</v>
-      </c>
-      <c r="K34" s="6" t="n">
-        <v>46153</v>
+      <c r="K34" s="3" t="n">
+        <v>46185</v>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
@@ -2231,100 +2228,100 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>OPP-1074</t>
+          <t>OPP-1234</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Delvecchio Packaging</t>
+          <t>Tharnwick Rail</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Conveyor presence detection</t>
+          <t>RV-2 trackside trial</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>ProximaSense X4</t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="n">
-        <v>150</v>
-      </c>
-      <c r="F35" s="4" t="n">
-        <v>7800</v>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>Qualification</t>
-        </is>
-      </c>
-      <c r="H35" s="5" t="n">
+          <t>RV-2</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>209</v>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>3344</v>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>Discovery</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="n">
         <v>0.1</v>
       </c>
-      <c r="I35" s="2" t="inlineStr">
+      <c r="J35" s="2" t="inlineStr">
         <is>
           <t>Pipeline</t>
         </is>
       </c>
-      <c r="J35" s="6" t="n">
-        <v>46091</v>
-      </c>
-      <c r="K35" s="6" t="n">
-        <v>46199</v>
+      <c r="K35" s="3" t="n">
+        <v>46276</v>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>Jamal</t>
+          <t>Elena</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>OPP-1075</t>
+          <t>OPP-1235</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Coldharbour Logistics</t>
+          <t>Tessivex</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Pump and compressor monitoring</t>
+          <t>MX-3 service stock</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>FieldSense 200</t>
-        </is>
-      </c>
-      <c r="E36" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="F36" s="4" t="n">
-        <v>32000</v>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>Qualification</t>
-        </is>
-      </c>
-      <c r="H36" s="5" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>Pipeline</t>
-        </is>
-      </c>
-      <c r="J36" s="6" t="n">
-        <v>46092</v>
-      </c>
-      <c r="K36" s="6" t="n">
-        <v>46164</v>
+          <t>MX-3</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>238.5</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>7155</v>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>Proposal</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="n">
+        <v>46142</v>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
@@ -2335,256 +2332,256 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>OPP-1076</t>
+          <t>OPP-1236</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Oakhurst Tanning</t>
+          <t>Oskerry Systems</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Outdoor tank level monitoring</t>
+          <t>GX-7 integration kit</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>XT-9</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="F37" s="4" t="n">
-        <v>17400</v>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
+          <t>GX-7</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="F37" s="2" t="n">
+        <v>215.1</v>
+      </c>
+      <c r="G37" s="2" t="n">
+        <v>8604</v>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>Qualification</t>
         </is>
       </c>
-      <c r="H37" s="5" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
+      <c r="I37" s="2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
         <is>
           <t>Pipeline</t>
         </is>
       </c>
-      <c r="J37" s="6" t="n">
-        <v>46093</v>
-      </c>
-      <c r="K37" s="6" t="n">
-        <v>46167</v>
+      <c r="K37" s="3" t="n">
+        <v>46199</v>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>Elena</t>
+          <t>Jamal</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>OPP-1077</t>
+          <t>OPP-1237</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Radley Composites</t>
+          <t>Fenstad Systems</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Pump and compressor monitoring</t>
+          <t>MX-3 pilot units</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>FieldSense 200</t>
-        </is>
-      </c>
-      <c r="E38" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="F38" s="4" t="n">
-        <v>6720</v>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>Qualification</t>
-        </is>
-      </c>
-      <c r="H38" s="5" t="n">
+          <t>MX-3</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>238.5</v>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>4770</v>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>Discovery</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="n">
         <v>0.1</v>
       </c>
-      <c r="I38" s="2" t="inlineStr">
+      <c r="J38" s="2" t="inlineStr">
         <is>
           <t>Pipeline</t>
         </is>
       </c>
-      <c r="J38" s="6" t="n">
-        <v>46093</v>
-      </c>
-      <c r="K38" s="6" t="n">
-        <v>46195</v>
+      <c r="K38" s="3" t="n">
+        <v>46295</v>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>Jamal</t>
+          <t>Elena</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>OPP-1078</t>
+          <t>OPP-1238</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Whitlow Dairy</t>
+          <t>Pellowdine Industrial</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Rotating equipment monitoring</t>
+          <t>RV-2 evaluation units</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>FieldSense 200</t>
-        </is>
-      </c>
-      <c r="E39" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="F39" s="4" t="n">
-        <v>10080</v>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>Qualification</t>
-        </is>
-      </c>
-      <c r="H39" s="5" t="n">
+          <t>RV-2</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F39" s="2" t="n">
+        <v>209</v>
+      </c>
+      <c r="G39" s="2" t="n">
+        <v>2090</v>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>Discovery</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="n">
         <v>0.1</v>
       </c>
-      <c r="I39" s="2" t="inlineStr">
+      <c r="J39" s="2" t="inlineStr">
         <is>
           <t>Pipeline</t>
         </is>
       </c>
-      <c r="J39" s="6" t="n">
-        <v>46094</v>
-      </c>
-      <c r="K39" s="6" t="n">
-        <v>46199</v>
+      <c r="K39" s="3" t="n">
+        <v>46311</v>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>Jamal</t>
+          <t>Elena</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>OPP-1079</t>
+          <t>OPP-1239</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Carver Automation</t>
+          <t>Quennick</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>FieldSense 200 integrator evaluation</t>
+          <t>RV-2 evaluation units</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>FieldSense 200</t>
-        </is>
-      </c>
-      <c r="E40" s="3" t="n">
-        <v>120</v>
-      </c>
-      <c r="F40" s="4" t="n">
-        <v>96000</v>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>Demo / evaluation</t>
-        </is>
-      </c>
-      <c r="H40" s="5" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>Commit</t>
-        </is>
-      </c>
-      <c r="J40" s="6" t="n">
-        <v>46097</v>
-      </c>
-      <c r="K40" s="6" t="n">
-        <v>46171</v>
+          <t>RV-2</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F40" s="2" t="n">
+        <v>189</v>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>2268</v>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>Qualification</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>Pipeline</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="n">
+        <v>46192</v>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>Jamal</t>
+          <t>Elena</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>OPP-1080</t>
+          <t>OPP-1240</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Lindqvist Marine</t>
+          <t>Trellisar</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Boiler room instrumentation</t>
+          <t>GX-7 spares pool</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>XT-9</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="F41" s="4" t="n">
-        <v>14500</v>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>Qualification</t>
-        </is>
-      </c>
-      <c r="H41" s="5" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>Pipeline</t>
-        </is>
-      </c>
-      <c r="J41" s="6" t="n">
-        <v>46098</v>
-      </c>
-      <c r="K41" s="6" t="n">
-        <v>46177</v>
+          <t>GX-7</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="F41" s="2" t="n">
+        <v>192.6</v>
+      </c>
+      <c r="G41" s="2" t="n">
+        <v>5778</v>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>Proposal</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="n">
+        <v>46150</v>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
@@ -2595,48 +2592,48 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>OPP-1081</t>
+          <t>OPP-1241</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Stanmore Polymers</t>
+          <t>Ivelmoor Group</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Rotating equipment monitoring</t>
+          <t>GX-7 panel retrofit</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>FieldSense 200</t>
-        </is>
-      </c>
-      <c r="E42" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="F42" s="4" t="n">
-        <v>10080</v>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>Qualification</t>
-        </is>
-      </c>
-      <c r="H42" s="5" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>Pipeline</t>
-        </is>
-      </c>
-      <c r="J42" s="6" t="n">
-        <v>46098</v>
-      </c>
-      <c r="K42" s="6" t="n">
-        <v>46157</v>
+          <t>GX-7</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>192.6</v>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>10593</v>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>Negotiation</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="n">
+        <v>46141</v>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
@@ -2647,48 +2644,48 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>OPP-1082</t>
+          <t>OPP-1242</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Duvall Hydro</t>
+          <t>Kilnwarden Utilities</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>FieldSense 200 pilot</t>
+          <t>MX-3 spares</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>FieldSense 200</t>
-        </is>
-      </c>
-      <c r="E43" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="F43" s="4" t="n">
-        <v>20000</v>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>Qualification</t>
-        </is>
-      </c>
-      <c r="H43" s="5" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>Pipeline</t>
-        </is>
-      </c>
-      <c r="J43" s="6" t="n">
-        <v>46101</v>
-      </c>
-      <c r="K43" s="6" t="n">
-        <v>46178</v>
+          <t>MX-3</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="F43" s="2" t="n">
+        <v>238.5</v>
+      </c>
+      <c r="G43" s="2" t="n">
+        <v>4770</v>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>Negotiation</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="n">
+        <v>46127</v>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
@@ -2699,48 +2696,48 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>OPP-1083</t>
+          <t>OPP-1243</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Prescott Mills</t>
+          <t>Sorrelby Water</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Boiler room instrumentation</t>
+          <t>GX-7 intake station</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>XT-9</t>
-        </is>
-      </c>
-      <c r="E44" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="F44" s="4" t="n">
-        <v>12160</v>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>Qualification</t>
-        </is>
-      </c>
-      <c r="H44" s="5" t="n">
+          <t>GX-7</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="F44" s="2" t="n">
+        <v>215.1</v>
+      </c>
+      <c r="G44" s="2" t="n">
+        <v>9679.5</v>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>Discovery</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="n">
         <v>0.1</v>
       </c>
-      <c r="I44" s="2" t="inlineStr">
+      <c r="J44" s="2" t="inlineStr">
         <is>
           <t>Pipeline</t>
         </is>
       </c>
-      <c r="J44" s="6" t="n">
-        <v>46103</v>
-      </c>
-      <c r="K44" s="6" t="n">
-        <v>46171</v>
+      <c r="K44" s="3" t="n">
+        <v>46241</v>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
@@ -2751,48 +2748,48 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>OPP-1084</t>
+          <t>OPP-1244</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Blackmoor Energy</t>
+          <t>Drossick</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>High-temperature pipeline station monitoring</t>
+          <t>MX-3 plant two</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>FieldSense 200</t>
-        </is>
-      </c>
-      <c r="E45" s="3" t="n">
-        <v>375</v>
-      </c>
-      <c r="F45" s="4" t="n">
-        <v>300000</v>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>Discovery</t>
-        </is>
-      </c>
-      <c r="H45" s="5" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>Best Case</t>
-        </is>
-      </c>
-      <c r="J45" s="6" t="n">
-        <v>46104</v>
-      </c>
-      <c r="K45" s="6" t="n">
-        <v>46199</v>
+          <t>MX-3</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="F45" s="2" t="n">
+        <v>238.5</v>
+      </c>
+      <c r="G45" s="2" t="n">
+        <v>14310</v>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>Qualification</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>Pipeline</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="n">
+        <v>46178</v>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
@@ -2803,48 +2800,48 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>OPP-1085</t>
+          <t>OPP-1245</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Cresswell Plating</t>
+          <t>Hessanby Dynamics</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Bin level detection</t>
+          <t>MX-3 test cell</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>ProximaSense X4</t>
-        </is>
-      </c>
-      <c r="E46" s="3" t="n">
-        <v>80</v>
-      </c>
-      <c r="F46" s="4" t="n">
-        <v>4640</v>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t>Qualification</t>
-        </is>
-      </c>
-      <c r="H46" s="5" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I46" s="2" t="inlineStr">
+          <t>MX-3</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="F46" s="2" t="n">
+        <v>238.5</v>
+      </c>
+      <c r="G46" s="2" t="n">
+        <v>4293</v>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>Evaluation</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
         <is>
           <t>Pipeline</t>
         </is>
       </c>
-      <c r="J46" s="6" t="n">
-        <v>46109</v>
-      </c>
-      <c r="K46" s="6" t="n">
-        <v>46168</v>
+      <c r="K46" s="3" t="n">
+        <v>46162</v>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
@@ -2863,18 +2860,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="39" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="7" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="31" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="26" customWidth="1" min="8" max="8"/>
-    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
   </cols>
@@ -2944,40 +2941,40 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Delvecchio Packaging</t>
+          <t>Quennick</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>ProximaSense X4 initial deployment</t>
+          <t>MX-3 February batch</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>ProximaSense X4</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="n">
-        <v>400</v>
-      </c>
-      <c r="F2" s="4" t="n">
-        <v>49</v>
-      </c>
-      <c r="G2" s="4" t="n">
-        <v>19600</v>
-      </c>
-      <c r="H2" s="6" t="n">
-        <v>45950</v>
-      </c>
-      <c r="I2" s="6" t="n">
-        <v>46031</v>
+          <t>MX-3</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>312</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>238.5</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>74412</v>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>45944</v>
+      </c>
+      <c r="I2" s="3" t="n">
+        <v>46036</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>Jamal</t>
+          <t>Elena</t>
         </is>
       </c>
     </row>
@@ -2989,40 +2986,40 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Brannock Refinery</t>
+          <t>Sorrelby Water</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>XT-9 tank level monitoring, phase 1</t>
+          <t>GX-7 treatment works, phase 1</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>XT-9</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>36</v>
-      </c>
-      <c r="F3" s="4" t="n">
-        <v>1450</v>
-      </c>
-      <c r="G3" s="4" t="n">
-        <v>52200</v>
-      </c>
-      <c r="H3" s="6" t="n">
-        <v>45964</v>
-      </c>
-      <c r="I3" s="6" t="n">
-        <v>46038</v>
+          <t>GX-7</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>160</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>192.6</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>30816</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>45922</v>
+      </c>
+      <c r="I3" s="3" t="n">
+        <v>46031</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>74</v>
+        <v>109</v>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>Elena</t>
+          <t>Jamal</t>
         </is>
       </c>
     </row>
@@ -3034,36 +3031,36 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Whitlow Dairy</t>
+          <t>Kilnwarden Utilities</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Silo level sensing</t>
+          <t>MX-3 substation pilot</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>XT-9</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="F4" s="4" t="n">
-        <v>1450</v>
-      </c>
-      <c r="G4" s="4" t="n">
-        <v>34800</v>
-      </c>
-      <c r="H4" s="6" t="n">
-        <v>45978</v>
-      </c>
-      <c r="I4" s="6" t="n">
+          <t>MX-3</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>238.5</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>9540</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>45964</v>
+      </c>
+      <c r="I4" s="3" t="n">
         <v>46043</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
@@ -3079,40 +3076,40 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Stanmore Polymers</t>
+          <t>Trellisar</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Reactor vessel level sensing</t>
+          <t>GX-7 initial deployment</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>XT-9</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>48</v>
-      </c>
-      <c r="F5" s="4" t="n">
-        <v>1450</v>
-      </c>
-      <c r="G5" s="4" t="n">
-        <v>69600</v>
-      </c>
-      <c r="H5" s="6" t="n">
-        <v>45944</v>
-      </c>
-      <c r="I5" s="6" t="n">
+          <t>GX-7</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>180</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>192.6</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>34668</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>45936</v>
+      </c>
+      <c r="I5" s="3" t="n">
         <v>46050</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>Elena</t>
+          <t>Jamal</t>
         </is>
       </c>
     </row>
@@ -3124,36 +3121,36 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Ostergaard Process Systems</t>
+          <t>Pemberlith Foods</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>FieldSense 200 trial order</t>
+          <t>MX-3 packing line one</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>FieldSense 200</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="F6" s="4" t="n">
-        <v>800</v>
-      </c>
-      <c r="G6" s="4" t="n">
-        <v>32000</v>
-      </c>
-      <c r="H6" s="6" t="n">
-        <v>46034</v>
-      </c>
-      <c r="I6" s="6" t="n">
-        <v>46052</v>
+          <t>MX-3</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>110</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>238.5</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>26235</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>45978</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>46057</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>18</v>
+        <v>79</v>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
@@ -3169,36 +3166,36 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Tallis Water Authority</t>
+          <t>Ivelmoor Group</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Reservoir level monitoring phase 1</t>
+          <t>GX-7 plant one</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>XT-9</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>96</v>
-      </c>
-      <c r="F7" s="4" t="n">
-        <v>1450</v>
-      </c>
-      <c r="G7" s="4" t="n">
-        <v>139200</v>
-      </c>
-      <c r="H7" s="6" t="n">
-        <v>45943</v>
-      </c>
-      <c r="I7" s="6" t="n">
+          <t>GX-7</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>240</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>192.6</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>46224</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>45908</v>
+      </c>
+      <c r="I7" s="3" t="n">
         <v>46059</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>116</v>
+        <v>151</v>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
@@ -3214,36 +3211,36 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Fenwick Aggregates</t>
+          <t>Callowmere Packaging</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Conveyor presence detection</t>
+          <t>MX-3 line one</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>ProximaSense X4</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="F8" s="4" t="n">
-        <v>58</v>
-      </c>
-      <c r="G8" s="4" t="n">
-        <v>2900</v>
-      </c>
-      <c r="H8" s="6" t="n">
+          <t>MX-3</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>238.5</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>20272.5</v>
+      </c>
+      <c r="H8" s="3" t="n">
         <v>45992</v>
       </c>
-      <c r="I8" s="6" t="n">
-        <v>46064</v>
+      <c r="I8" s="3" t="n">
+        <v>46066</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
@@ -3259,36 +3256,36 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Nettleton Water</t>
+          <t>Tessivex</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Pump station level sensors</t>
+          <t>GX-7 evaluation units</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>XT-9</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="F9" s="4" t="n">
-        <v>1450</v>
-      </c>
-      <c r="G9" s="4" t="n">
-        <v>43500</v>
-      </c>
-      <c r="H9" s="6" t="n">
-        <v>45985</v>
-      </c>
-      <c r="I9" s="6" t="n">
+          <t>GX-7</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>214</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>2568</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>46034</v>
+      </c>
+      <c r="I9" s="3" t="n">
         <v>46071</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>86</v>
+        <v>37</v>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
@@ -3304,36 +3301,36 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Duvall Hydro</t>
+          <t>Tharnwick Rail</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Penstock and forebay level monitoring</t>
+          <t>MX-3 cabinet pilot</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>XT-9</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="F10" s="4" t="n">
-        <v>1450</v>
-      </c>
-      <c r="G10" s="4" t="n">
-        <v>58000</v>
-      </c>
-      <c r="H10" s="6" t="n">
-        <v>45992</v>
-      </c>
-      <c r="I10" s="6" t="n">
+          <t>MX-3</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>238.5</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>14310</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>45999</v>
+      </c>
+      <c r="I10" s="3" t="n">
         <v>46078</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
@@ -3349,36 +3346,36 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Barrow Tide Ports</t>
+          <t>Drossick</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Quay tank level monitoring</t>
+          <t>GX-7 plant one</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>XT-9</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="n">
-        <v>44</v>
-      </c>
-      <c r="F11" s="4" t="n">
-        <v>1450</v>
-      </c>
-      <c r="G11" s="4" t="n">
-        <v>63800</v>
-      </c>
-      <c r="H11" s="6" t="n">
-        <v>45994</v>
-      </c>
-      <c r="I11" s="6" t="n">
-        <v>46083</v>
+          <t>GX-7</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>110</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>181.9</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>20009</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>45985</v>
+      </c>
+      <c r="I11" s="3" t="n">
+        <v>46080</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
@@ -3394,32 +3391,32 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Ironbridge Foundry</t>
+          <t>Quennick</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Furnace area proximity sensing</t>
+          <t>GX-7 first site</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>ProximaSense X4</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="n">
-        <v>125</v>
-      </c>
-      <c r="F12" s="4" t="n">
-        <v>52</v>
-      </c>
-      <c r="G12" s="4" t="n">
-        <v>6500</v>
-      </c>
-      <c r="H12" s="6" t="n">
+          <t>GX-7</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>220</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>192.6</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>42372</v>
+      </c>
+      <c r="H12" s="3" t="n">
         <v>46006</v>
       </c>
-      <c r="I12" s="6" t="n">
+      <c r="I12" s="3" t="n">
         <v>46085</v>
       </c>
       <c r="J12" s="2" t="n">
@@ -3427,7 +3424,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>Jamal</t>
+          <t>Elena</t>
         </is>
       </c>
     </row>
@@ -3439,36 +3436,36 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Kessler Paper Mill</t>
+          <t>Kilnwarden Utilities</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Stock chest level sensors</t>
+          <t>GX-7 control room</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>XT-9</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="F13" s="4" t="n">
-        <v>1450</v>
-      </c>
-      <c r="G13" s="4" t="n">
-        <v>58000</v>
-      </c>
-      <c r="H13" s="6" t="n">
-        <v>45971</v>
-      </c>
-      <c r="I13" s="6" t="n">
+          <t>GX-7</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>214</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>7490</v>
+      </c>
+      <c r="H13" s="3" t="n">
+        <v>46041</v>
+      </c>
+      <c r="I13" s="3" t="n">
         <v>46087</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>116</v>
+        <v>46</v>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
@@ -3484,40 +3481,40 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Sable Creek Gas</t>
+          <t>Trellisar</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Wellhead tank monitoring</t>
+          <t>MX-3 service stock</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>XT-9</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="n">
-        <v>120</v>
-      </c>
-      <c r="F14" s="4" t="n">
-        <v>1450</v>
-      </c>
-      <c r="G14" s="4" t="n">
-        <v>174000</v>
-      </c>
-      <c r="H14" s="6" t="n">
-        <v>45957</v>
-      </c>
-      <c r="I14" s="6" t="n">
+          <t>MX-3</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>238.5</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>5962.5</v>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>46055</v>
+      </c>
+      <c r="I14" s="3" t="n">
         <v>46092</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>135</v>
+        <v>37</v>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>Elena</t>
+          <t>Jamal</t>
         </is>
       </c>
     </row>
@@ -3529,32 +3526,32 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Grayson Textiles</t>
+          <t>Pemberlith Foods</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Dye vat level sensing</t>
+          <t>GX-7 dispatch area</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>XT-9</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="F15" s="4" t="n">
-        <v>1520</v>
-      </c>
-      <c r="G15" s="4" t="n">
-        <v>7600</v>
-      </c>
-      <c r="H15" s="6" t="n">
+          <t>GX-7</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>214</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>8560</v>
+      </c>
+      <c r="H15" s="3" t="n">
         <v>46048</v>
       </c>
-      <c r="I15" s="6" t="n">
+      <c r="I15" s="3" t="n">
         <v>46094</v>
       </c>
       <c r="J15" s="2" t="n">
@@ -3574,36 +3571,36 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Quenby Plastics</t>
+          <t>Sorrelby Water</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Hopper level detection</t>
+          <t>MX-3 pumping station</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>XT-9</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="F16" s="4" t="n">
-        <v>1450</v>
-      </c>
-      <c r="G16" s="4" t="n">
-        <v>26100</v>
-      </c>
-      <c r="H16" s="6" t="n">
-        <v>46036</v>
-      </c>
-      <c r="I16" s="6" t="n">
-        <v>46101</v>
+          <t>MX-3</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>238.5</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>13117.5</v>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>46027</v>
+      </c>
+      <c r="I16" s="3" t="n">
+        <v>46099</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
@@ -3619,40 +3616,40 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Meridian Industrial</t>
+          <t>Oskerry Systems</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>XT-9 pilot, Dayton plant</t>
+          <t>GX-7 beta programme units</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>XT-9</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="F17" s="4" t="n">
-        <v>1450</v>
-      </c>
-      <c r="G17" s="4" t="n">
-        <v>34800</v>
-      </c>
-      <c r="H17" s="6" t="n">
-        <v>46001</v>
-      </c>
-      <c r="I17" s="6" t="n">
-        <v>46104</v>
+          <t>GX-7</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>214</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>4280</v>
+      </c>
+      <c r="H17" s="3" t="n">
+        <v>46062</v>
+      </c>
+      <c r="I17" s="3" t="n">
+        <v>46101</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>103</v>
+        <v>39</v>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>Elena</t>
+          <t>Jamal</t>
         </is>
       </c>
     </row>
@@ -3664,40 +3661,40 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Thornbury Power</t>
+          <t>Tessivex</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Condensate tank monitoring</t>
+          <t>MX-3 plant spares</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>XT-9</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="n">
-        <v>80</v>
-      </c>
-      <c r="F18" s="4" t="n">
-        <v>1450</v>
-      </c>
-      <c r="G18" s="4" t="n">
-        <v>116000</v>
-      </c>
-      <c r="H18" s="6" t="n">
-        <v>45999</v>
-      </c>
-      <c r="I18" s="6" t="n">
+          <t>MX-3</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>238.5</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>7155</v>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>46069</v>
+      </c>
+      <c r="I18" s="3" t="n">
         <v>46105</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>106</v>
+        <v>36</v>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>Elena</t>
+          <t>Jamal</t>
         </is>
       </c>
     </row>
@@ -3709,83 +3706,38 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Harrowgate Cement</t>
+          <t>Hessanby Dynamics</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Silo level instrumentation</t>
+          <t>GX-7 initial order</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>XT-9</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="n">
-        <v>80</v>
-      </c>
-      <c r="F19" s="4" t="n">
-        <v>1450</v>
-      </c>
-      <c r="G19" s="4" t="n">
-        <v>116000</v>
-      </c>
-      <c r="H19" s="6" t="n">
-        <v>45978</v>
-      </c>
-      <c r="I19" s="6" t="n">
+          <t>GX-7</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>198</v>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>17820</v>
+      </c>
+      <c r="H19" s="3" t="n">
+        <v>46029</v>
+      </c>
+      <c r="I19" s="3" t="n">
         <v>46107</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>129</v>
+        <v>78</v>
       </c>
       <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>Jamal</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>CW-2619</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>Marrowfield Foods</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>Tank farm level monitoring</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>XT-9</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="F20" s="4" t="n">
-        <v>1450</v>
-      </c>
-      <c r="G20" s="4" t="n">
-        <v>58000</v>
-      </c>
-      <c r="H20" s="6" t="n">
-        <v>46043</v>
-      </c>
-      <c r="I20" s="6" t="n">
-        <v>46108</v>
-      </c>
-      <c r="J20" s="2" t="n">
-        <v>65</v>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>Jamal</t>
         </is>
@@ -3870,28 +3822,28 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" s="4" t="n">
-        <v>226000</v>
-      </c>
-      <c r="D2" s="4" t="n">
-        <v>169500</v>
-      </c>
-      <c r="E2" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>101029.5</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>76053.60000000001</v>
+      </c>
+      <c r="E2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="F2" s="4" t="n">
-        <v>226000</v>
-      </c>
-      <c r="G2" s="4" t="n">
-        <v>300000</v>
-      </c>
-      <c r="H2" s="4" t="n">
-        <v>526000</v>
-      </c>
-      <c r="I2" s="4" t="n">
-        <v>300000</v>
+      <c r="F2" s="2" t="n">
+        <v>77179.5</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>79000</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>155053.6</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>140743.6</v>
       </c>
     </row>
     <row r="3">
@@ -3901,28 +3853,28 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="C3" s="4" t="n">
-        <v>514000</v>
-      </c>
-      <c r="D3" s="4" t="n">
-        <v>293900</v>
-      </c>
-      <c r="E3" s="4" t="n">
-        <v>190610</v>
-      </c>
-      <c r="F3" s="4" t="n">
-        <v>282000</v>
-      </c>
-      <c r="G3" s="4" t="n">
-        <v>314000</v>
-      </c>
-      <c r="H3" s="4" t="n">
-        <v>596000</v>
-      </c>
-      <c r="I3" s="4" t="n">
-        <v>596000</v>
+        <v>9</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>181954.2</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>110940.42</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>57780</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>81000</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>191940.42</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>127224</v>
       </c>
     </row>
     <row r="4">
@@ -3934,26 +3886,26 @@
       <c r="B4" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="C4" s="4" t="n">
-        <v>1360000</v>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>417600</v>
-      </c>
-      <c r="E4" s="4" t="n">
-        <v>264500</v>
-      </c>
-      <c r="F4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="4" t="n">
-        <v>328000</v>
-      </c>
-      <c r="H4" s="4" t="n">
-        <v>328000</v>
-      </c>
-      <c r="I4" s="4" t="n">
-        <v>328000</v>
+      <c r="C4" s="2" t="n">
+        <v>158980.5</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>81592.2</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>39423</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>22680</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>84000</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>165592.2</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>102144</v>
       </c>
     </row>
     <row r="5">
@@ -3963,28 +3915,28 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>2100000</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>881000</v>
-      </c>
-      <c r="E5" s="4" t="n">
-        <v>455110</v>
-      </c>
-      <c r="F5" s="4" t="n">
-        <v>508000</v>
-      </c>
-      <c r="G5" s="4" t="n">
-        <v>942000</v>
-      </c>
-      <c r="H5" s="4" t="n">
-        <v>1450000</v>
-      </c>
-      <c r="I5" s="4" t="n">
-        <v>1224000</v>
+        <v>23</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>441964.2</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>268586.22</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>39423</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>157639.5</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>244000</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>512586.22</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>370111.6</v>
       </c>
     </row>
   </sheetData>
